--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BYSPANIA TÍJOLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BYSPANIA TÍJOLA.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9231</v>
+        <v>4.9878</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1733</v>
+        <v>5.604</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2502</v>
+        <v>-0.6163</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4155</v>
+        <v>-0.4213</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0469</v>
+        <v>0.0292</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4624</v>
+        <v>-0.4506</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8505</v>
+        <v>3.0719</v>
       </c>
       <c r="K2" t="n">
-        <v>2.283</v>
+        <v>2.4068</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5675</v>
+        <v>0.6651</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.266</v>
+        <v>-3.4932</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2361</v>
+        <v>-2.3776</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0299</v>
+        <v>-1.1157</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1807</v>
+        <v>-0.1762</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0556</v>
+        <v>-0.9958</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8749</v>
+        <v>0.8196</v>
       </c>
       <c r="V2" t="n">
-        <v>4.1189</v>
+        <v>4.2221</v>
       </c>
       <c r="W2" t="n">
-        <v>4.3787</v>
+        <v>4.5016</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.096</v>
+        <v>2.0049</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1906</v>
+        <v>1.2577</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9054</v>
+        <v>0.7472</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4492</v>
+        <v>0.4261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9935</v>
+        <v>0.9821</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5443</v>
+        <v>-0.556</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0215</v>
+        <v>1.0787</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5796</v>
+        <v>1.6216</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5429</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5723</v>
+        <v>-0.6526</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4261</v>
+        <v>0.4173</v>
       </c>
       <c r="T3" t="n">
-        <v>0.169</v>
+        <v>0.1791</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2571</v>
+        <v>0.2382</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6801</v>
+        <v>1.5987</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9115</v>
+        <v>1.1144</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7685</v>
+        <v>0.4843</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6688</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0666</v>
+        <v>1.0761</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7354</v>
+        <v>-1.754</v>
       </c>
       <c r="J4" t="n">
-        <v>0.669</v>
+        <v>0.8338</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9031</v>
+        <v>2.0168</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2341</v>
+        <v>-1.183</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3377</v>
+        <v>-1.5117</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8365</v>
+        <v>-0.9407</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5013</v>
+        <v>-0.571</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0087</v>
+        <v>2.9455</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2432</v>
+        <v>2.228</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7175</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
@@ -799,28 +799,28 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2656</v>
+        <v>-0.2837</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0445</v>
+        <v>-0.0413</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2211</v>
+        <v>-0.2424</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -844,22 +844,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0258</v>
+        <v>-0.0247</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0387</v>
+        <v>0.0371</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4222</v>
+        <v>-0.4256</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5075</v>
+        <v>-0.4173</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0853</v>
+        <v>-0.0083</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2331</v>
+        <v>-0.2487</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1267</v>
+        <v>-1.1282</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6816</v>
+        <v>0.7302</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2796</v>
+        <v>1.3137</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9147</v>
+        <v>-0.9789</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3861</v>
+        <v>-0.4342</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5447</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3092</v>
+        <v>-0.2938</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.509</v>
+        <v>-0.4854</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1998</v>
+        <v>0.1917</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5546</v>
+        <v>-0.5192</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3325</v>
+        <v>1.6327</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8871</v>
+        <v>-2.152</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0374</v>
+        <v>0.0668</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2266</v>
+        <v>1.2403</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1892</v>
+        <v>-1.1735</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3884</v>
+        <v>3.6022</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5408</v>
+        <v>3.6666</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1524</v>
+        <v>-0.0643</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.351</v>
+        <v>-3.5354</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3142</v>
+        <v>-2.4263</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0368</v>
+        <v>-1.1091</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0245</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0554</v>
+        <v>-0.0221</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0633</v>
+        <v>0.0466</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9717</v>
+        <v>-0.9656</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9786</v>
+        <v>-1.9108</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0068</v>
+        <v>0.9452</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.454</v>
+        <v>-2.4146</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4737</v>
+        <v>-0.4485</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9803</v>
+        <v>-1.9661</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.3321</v>
+        <v>-2.2686</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0161</v>
+        <v>-0.9801</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.316</v>
+        <v>-1.2885</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6643</v>
+        <v>-0.6776</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5623</v>
+        <v>1.5269</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0337</v>
+        <v>1.0198</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5285</v>
+        <v>0.507</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7815</v>
+        <v>-2.579</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3084</v>
+        <v>-0.7876</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4731</v>
+        <v>-1.7914</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.8333</v>
+        <v>-4.6985</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.1941</v>
+        <v>-4.1544</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6392</v>
+        <v>-0.5441</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4317</v>
+        <v>-1.0723</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6869</v>
+        <v>-1.511</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2552</v>
+        <v>0.4387</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4016</v>
+        <v>-3.6262</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5073</v>
+        <v>-2.6434</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8943</v>
+        <v>-0.9828</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.128</v>
+        <v>-1.0821</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8556</v>
+        <v>-0.8011</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2724</v>
+        <v>-0.281</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3793</v>
+        <v>1.449</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9791</v>
+        <v>2.0595</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4856</v>
+        <v>-4.567</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5955</v>
+        <v>-2.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8901</v>
+        <v>-2.1669</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.7692</v>
+        <v>-6.7725</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.5158</v>
+        <v>-4.5162</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2534</v>
+        <v>-2.2564</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.2826</v>
+        <v>-3.1042</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9304</v>
+        <v>-1.8241</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3522</v>
+        <v>-1.2801</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.4866</v>
+        <v>-3.6683</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.5854</v>
+        <v>-2.6921</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9012</v>
+        <v>-0.9762</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1431</v>
+        <v>1.1219</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6871</v>
+        <v>0.7042</v>
       </c>
       <c r="U10" t="n">
-        <v>0.456</v>
+        <v>0.4177</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8063</v>
+        <v>-5.8591</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9642</v>
+        <v>-2.7557</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.842</v>
+        <v>-3.1034</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9793</v>
+        <v>-3.0437</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8087</v>
+        <v>-2.8393</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1706</v>
+        <v>-0.2044</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4923</v>
+        <v>-1.407</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8943</v>
+        <v>-0.8235</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.487</v>
+        <v>-1.6367</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9143</v>
+        <v>-2.0157</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4274</v>
+        <v>0.379</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0533</v>
+        <v>1.0414</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0094</v>
+        <v>1.0134</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0439</v>
+        <v>0.028</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4799</v>
+        <v>-2.4937</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.588299999999999</v>
+        <v>-6.607799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7907999999999995</v>
+        <v>1.2961</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.797600000000001</v>
+        <v>-7.904</v>
       </c>
       <c r="G12" t="n">
-        <v>-17.8466</v>
+        <v>-17.7638</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.7451</v>
+        <v>-7.730700000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-10.1015</v>
+        <v>-10.0333</v>
       </c>
       <c r="J12" t="n">
-        <v>0.09230000000000049</v>
+        <v>1.485199999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>5.078399999999999</v>
+        <v>5.9073</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.986</v>
+        <v>-4.422</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.9388</v>
+        <v>-19.249</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.8235</v>
+        <v>-13.6378</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.115400000000001</v>
+        <v>-5.6112</v>
       </c>
       <c r="P12" t="n">
-        <v>5.0014</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.002699999999999</v>
+        <v>-8.763199999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>14.0041</v>
+        <v>13.6315</v>
       </c>
       <c r="S12" t="n">
-        <v>5.557700000000001</v>
+        <v>5.5007</v>
       </c>
       <c r="T12" t="n">
-        <v>2.602300000000001</v>
+        <v>2.778300000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9554</v>
+        <v>2.7224</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6990000000000003</v>
+        <v>0.7867999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>5.517</v>
+        <v>5.7959</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.818</v>
+        <v>-5.009</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BYSPANIA TÍJOLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BYSPANIA TÍJOLA.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9878</v>
+        <v>5.867</v>
       </c>
       <c r="E2" t="n">
-        <v>5.604</v>
+        <v>6.6008</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6163</v>
+        <v>-0.7338</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4213</v>
@@ -610,13 +610,13 @@
         <v>2.3368</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1762</v>
+        <v>0.703</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9958</v>
+        <v>0.001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8196</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>4.2221</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0049</v>
+        <v>2.1657</v>
       </c>
       <c r="E3" t="n">
         <v>1.2577</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7472</v>
+        <v>0.9079</v>
       </c>
       <c r="G3" t="n">
         <v>0.4261</v>
@@ -688,13 +688,13 @@
         <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4173</v>
+        <v>0.578</v>
       </c>
       <c r="T3" t="n">
         <v>0.1791</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2382</v>
+        <v>0.3989</v>
       </c>
       <c r="V3" t="n">
         <v>0.3826</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5987</v>
+        <v>0.496</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1144</v>
+        <v>0.018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4843</v>
+        <v>0.4781</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6778999999999999</v>
@@ -766,13 +766,13 @@
         <v>1.5579</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9455</v>
+        <v>1.8429</v>
       </c>
       <c r="T4" t="n">
-        <v>2.228</v>
+        <v>1.1315</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7175</v>
+        <v>0.7113</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2795</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2837</v>
+        <v>0.3673</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0413</v>
+        <v>0.1807</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2424</v>
+        <v>0.1865</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0205</v>
+        <v>-0.2487</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0205</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-1.1282</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0205</v>
+        <v>0.7302</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0205</v>
+        <v>1.3137</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.5835</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.9789</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.4342</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0247</v>
+        <v>0.4991</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0618</v>
+        <v>0.1126</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0371</v>
+        <v>0.3865</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2795</v>
+        <v>-0.6621</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4256</v>
+        <v>0.1183</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4173</v>
+        <v>2.1311</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0083</v>
+        <v>-2.0128</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2487</v>
+        <v>0.0668</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8794999999999999</v>
+        <v>1.2403</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1282</v>
+        <v>-1.1735</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7302</v>
+        <v>3.6022</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3137</v>
+        <v>3.6666</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5835</v>
+        <v>-0.0643</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9789</v>
+        <v>-3.5354</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4342</v>
+        <v>-2.4263</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5447</v>
+        <v>-1.1091</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7789</v>
+        <v>1.9474</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2938</v>
+        <v>0.662</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4854</v>
+        <v>0.4763</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1917</v>
+        <v>0.1857</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6621</v>
+        <v>-0.6105</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5192</v>
+        <v>-0.228</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6327</v>
+        <v>-0.0413</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.152</v>
+        <v>-0.1867</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0668</v>
+        <v>0.0205</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2403</v>
+        <v>0.0205</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1735</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6022</v>
+        <v>0.0205</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6666</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0643</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.5354</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4263</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1091</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9474</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0245</v>
+        <v>0.0309</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0221</v>
+        <v>-0.0618</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0466</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6105</v>
+        <v>-0.2795</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6105</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9656</v>
+        <v>-1.2313</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9108</v>
+        <v>0.0098</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9452</v>
+        <v>-1.2411</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4146</v>
+        <v>-4.6985</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4485</v>
+        <v>-4.1544</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9661</v>
+        <v>-0.5441</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.2686</v>
+        <v>-1.0723</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9801</v>
+        <v>-1.511</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2885</v>
+        <v>0.4387</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.146</v>
+        <v>-3.6262</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5316</v>
+        <v>-2.6434</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6776</v>
+        <v>-0.9828</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.7526</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5842000000000001</v>
+        <v>2.7263</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5269</v>
+        <v>0.2656</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0198</v>
+        <v>-0.0037</v>
       </c>
       <c r="U8" t="n">
-        <v>0.507</v>
+        <v>0.2692</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6621</v>
+        <v>1.449</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6621</v>
+        <v>2.0595</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.579</v>
+        <v>-1.7306</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7876</v>
+        <v>-2.5089</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7914</v>
+        <v>0.7783</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6985</v>
+        <v>-2.4146</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.1544</v>
+        <v>-0.4485</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5441</v>
+        <v>-1.9661</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0723</v>
+        <v>-2.2686</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.511</v>
+        <v>-0.9801</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4387</v>
+        <v>-1.2885</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.6262</v>
+        <v>-0.146</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6434</v>
+        <v>0.5316</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9828</v>
+        <v>-0.6776</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7526</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7263</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0821</v>
+        <v>0.7619</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8011</v>
+        <v>0.4218</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.281</v>
+        <v>0.3401</v>
       </c>
       <c r="V9" t="n">
-        <v>1.449</v>
+        <v>-0.6621</v>
       </c>
       <c r="W9" t="n">
-        <v>2.0595</v>
+        <v>-0.6621</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.567</v>
+        <v>-5.5546</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4</v>
+        <v>-2.9981</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1669</v>
+        <v>-2.5565</v>
       </c>
       <c r="G10" t="n">
         <v>-6.7725</v>
@@ -1234,13 +1234,13 @@
         <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1219</v>
+        <v>0.1343</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7042</v>
+        <v>0.1062</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4177</v>
+        <v>0.0281</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2795</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8591</v>
+        <v>-6.2129</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7557</v>
+        <v>-3.3537</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1034</v>
+        <v>-2.8592</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0437</v>
@@ -1312,13 +1312,13 @@
         <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0414</v>
+        <v>0.6876</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0134</v>
+        <v>0.4153</v>
       </c>
       <c r="U11" t="n">
-        <v>0.028</v>
+        <v>0.2722</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4937</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.607799999999999</v>
+        <v>-5.943099999999999</v>
       </c>
       <c r="E12" t="n">
         <v>1.2961</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.904</v>
+        <v>-7.2393</v>
       </c>
       <c r="G12" t="n">
         <v>-17.7638</v>
@@ -1369,7 +1369,7 @@
         <v>5.9073</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.422</v>
+        <v>-4.422000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-19.249</v>
@@ -1390,13 +1390,13 @@
         <v>13.6315</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5007</v>
+        <v>6.1653</v>
       </c>
       <c r="T12" t="n">
-        <v>2.778300000000001</v>
+        <v>2.7783</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7224</v>
+        <v>3.3869</v>
       </c>
       <c r="V12" t="n">
         <v>0.7867999999999999</v>
